--- a/hj/demo/demo/导入服务模板 .xlsx
+++ b/hj/demo/demo/导入服务模板 .xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB39D37-BA98-44CB-A71F-809F5EE504B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85E4D87-F1B3-43BD-A19B-E8C229CE4381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="357">
   <si>
     <t>代理服务名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1126,6 +1126,324 @@
   </si>
   <si>
     <t>http://172.16.238.64:8015/15290001120010/DGR2034/B_SglFreqMeas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>站点名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MFID</t>
+    </r>
+  </si>
+  <si>
+    <t>经度</t>
+  </si>
+  <si>
+    <t>纬度</t>
+  </si>
+  <si>
+    <t>地址</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>设备型号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EQUID</t>
+    </r>
+  </si>
+  <si>
+    <t>集成厂商</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所属部门</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>负责人</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>联系方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>原子服务地址</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>业务类型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>服务类型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>报文格式</t>
+    </r>
+  </si>
+  <si>
+    <t>宋锦鸿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘佳欣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏文兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐开君</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李芮军</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1133,7 +1451,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1179,8 +1497,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1190,6 +1517,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1222,7 +1555,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1242,6 +1575,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1524,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S194"/>
+  <dimension ref="A1:S195"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.625" customWidth="1"/>
@@ -1544,49 +1881,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1">
-        <v>113.749549</v>
-      </c>
-      <c r="D1">
-        <v>42.269164000000004</v>
-      </c>
-      <c r="E1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K1">
-        <v>13947396696</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O1" t="s">
-        <v>98</v>
-      </c>
-      <c r="S1" s="2"/>
+      <c r="A1" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -1616,14 +1959,17 @@
       <c r="I2" t="s">
         <v>82</v>
       </c>
+      <c r="J2" t="s">
+        <v>352</v>
+      </c>
       <c r="K2">
         <v>13947396696</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
         <v>97</v>
@@ -1631,6 +1977,7 @@
       <c r="O2" t="s">
         <v>98</v>
       </c>
+      <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1660,14 +2007,17 @@
       <c r="I3" t="s">
         <v>82</v>
       </c>
+      <c r="J3" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K3">
         <v>13947396696</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N3" t="s">
         <v>97</v>
@@ -1704,14 +2054,17 @@
       <c r="I4" t="s">
         <v>82</v>
       </c>
+      <c r="J4" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K4">
         <v>13947396696</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s">
         <v>97</v>
@@ -1748,14 +2101,17 @@
       <c r="I5" t="s">
         <v>82</v>
       </c>
+      <c r="J5" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K5">
         <v>13947396696</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="N5" t="s">
         <v>97</v>
@@ -1792,14 +2148,17 @@
       <c r="I6" t="s">
         <v>82</v>
       </c>
+      <c r="J6" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K6">
         <v>13947396696</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M6" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s">
         <v>97</v>
@@ -1825,10 +2184,10 @@
         <v>92</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="G7" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s">
         <v>95</v>
@@ -1836,14 +2195,17 @@
       <c r="I7" t="s">
         <v>82</v>
       </c>
+      <c r="J7" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K7">
         <v>13947396696</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="M7" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N7" t="s">
         <v>97</v>
@@ -1880,14 +2242,17 @@
       <c r="I8" t="s">
         <v>82</v>
       </c>
+      <c r="J8" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K8">
         <v>13947396696</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N8" t="s">
         <v>97</v>
@@ -1924,14 +2289,17 @@
       <c r="I9" t="s">
         <v>82</v>
       </c>
+      <c r="J9" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K9">
         <v>13947396696</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N9" t="s">
         <v>97</v>
@@ -1968,14 +2336,17 @@
       <c r="I10" t="s">
         <v>82</v>
       </c>
+      <c r="J10" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K10">
         <v>13947396696</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="N10" t="s">
         <v>97</v>
@@ -2012,14 +2383,17 @@
       <c r="I11" t="s">
         <v>82</v>
       </c>
+      <c r="J11" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K11">
         <v>13947396696</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N11" t="s">
         <v>97</v>
@@ -2056,14 +2430,17 @@
       <c r="I12" t="s">
         <v>82</v>
       </c>
+      <c r="J12" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K12">
         <v>13947396696</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N12" t="s">
         <v>97</v>
@@ -2100,14 +2477,17 @@
       <c r="I13" t="s">
         <v>82</v>
       </c>
+      <c r="J13" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K13">
         <v>13947396696</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N13" t="s">
         <v>97</v>
@@ -2144,14 +2524,17 @@
       <c r="I14" t="s">
         <v>82</v>
       </c>
+      <c r="J14" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K14">
         <v>13947396696</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N14" t="s">
         <v>97</v>
@@ -2188,14 +2571,17 @@
       <c r="I15" t="s">
         <v>82</v>
       </c>
+      <c r="J15" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K15">
         <v>13947396696</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M15" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N15" t="s">
         <v>97</v>
@@ -2232,14 +2618,17 @@
       <c r="I16" t="s">
         <v>82</v>
       </c>
+      <c r="J16" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K16">
         <v>13947396696</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M16" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N16" t="s">
         <v>97</v>
@@ -2276,14 +2665,17 @@
       <c r="I17" t="s">
         <v>82</v>
       </c>
+      <c r="J17" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K17">
         <v>13947396696</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M17" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N17" t="s">
         <v>97</v>
@@ -2320,14 +2712,17 @@
       <c r="I18" t="s">
         <v>82</v>
       </c>
+      <c r="J18" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K18">
         <v>13947396696</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="M18" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="N18" t="s">
         <v>97</v>
@@ -2353,10 +2748,10 @@
         <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H19" t="s">
         <v>95</v>
@@ -2364,14 +2759,17 @@
       <c r="I19" t="s">
         <v>82</v>
       </c>
+      <c r="J19" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K19">
         <v>13947396696</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="M19" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="N19" t="s">
         <v>97</v>
@@ -2408,14 +2806,17 @@
       <c r="I20" t="s">
         <v>82</v>
       </c>
+      <c r="J20" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K20">
         <v>13947396696</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M20" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N20" t="s">
         <v>97</v>
@@ -2452,14 +2853,17 @@
       <c r="I21" t="s">
         <v>82</v>
       </c>
+      <c r="J21" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K21">
         <v>13947396696</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M21" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="N21" t="s">
         <v>97</v>
@@ -2485,10 +2889,10 @@
         <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H22" t="s">
         <v>95</v>
@@ -2496,14 +2900,17 @@
       <c r="I22" t="s">
         <v>82</v>
       </c>
+      <c r="J22" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K22">
         <v>13947396696</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="M22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N22" t="s">
         <v>97</v>
@@ -2540,14 +2947,17 @@
       <c r="I23" t="s">
         <v>82</v>
       </c>
+      <c r="J23" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K23">
         <v>13947396696</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N23" t="s">
         <v>97</v>
@@ -2584,14 +2994,17 @@
       <c r="I24" t="s">
         <v>82</v>
       </c>
+      <c r="J24" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K24">
         <v>13947396696</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N24" t="s">
         <v>97</v>
@@ -2628,14 +3041,17 @@
       <c r="I25" t="s">
         <v>82</v>
       </c>
+      <c r="J25" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K25">
         <v>13947396696</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="M25" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="N25" t="s">
         <v>97</v>
@@ -2672,14 +3088,17 @@
       <c r="I26" t="s">
         <v>82</v>
       </c>
+      <c r="J26" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K26">
         <v>13947396696</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N26" t="s">
         <v>97</v>
@@ -2716,14 +3135,17 @@
       <c r="I27" t="s">
         <v>82</v>
       </c>
+      <c r="J27" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K27">
         <v>13947396696</v>
       </c>
-      <c r="L27" t="s">
-        <v>125</v>
+      <c r="L27" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="M27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N27" t="s">
         <v>97</v>
@@ -2760,14 +3182,17 @@
       <c r="I28" t="s">
         <v>82</v>
       </c>
+      <c r="J28" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K28">
         <v>13947396696</v>
       </c>
-      <c r="L28" s="4" t="s">
-        <v>126</v>
+      <c r="L28" t="s">
+        <v>125</v>
       </c>
       <c r="M28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N28" t="s">
         <v>97</v>
@@ -2804,14 +3229,17 @@
       <c r="I29" t="s">
         <v>82</v>
       </c>
+      <c r="J29" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K29">
         <v>13947396696</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M29" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="N29" t="s">
         <v>97</v>
@@ -2848,14 +3276,17 @@
       <c r="I30" t="s">
         <v>82</v>
       </c>
+      <c r="J30" s="10" t="s">
+        <v>352</v>
+      </c>
       <c r="K30">
         <v>13947396696</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M30" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N30" t="s">
         <v>97</v>
@@ -2866,40 +3297,43 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C31">
-        <v>113.117768</v>
+        <v>113.749549</v>
       </c>
       <c r="D31">
-        <v>41.084122000000001</v>
+        <v>42.269164000000004</v>
       </c>
       <c r="E31" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="G31" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H31" t="s">
         <v>95</v>
       </c>
       <c r="I31" t="s">
-        <v>70</v>
-      </c>
-      <c r="K31" s="6">
-        <v>18604743099</v>
+        <v>82</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K31">
+        <v>13947396696</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="M31" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N31" t="s">
         <v>97</v>
@@ -2936,14 +3370,17 @@
       <c r="I32" t="s">
         <v>70</v>
       </c>
+      <c r="J32" t="s">
+        <v>353</v>
+      </c>
       <c r="K32" s="6">
         <v>18604743099</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M32" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N32" t="s">
         <v>97</v>
@@ -2980,14 +3417,17 @@
       <c r="I33" t="s">
         <v>70</v>
       </c>
+      <c r="J33" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K33" s="6">
         <v>18604743099</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N33" t="s">
         <v>97</v>
@@ -3024,14 +3464,17 @@
       <c r="I34" t="s">
         <v>70</v>
       </c>
+      <c r="J34" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K34" s="6">
         <v>18604743099</v>
       </c>
-      <c r="L34" s="7" t="s">
-        <v>137</v>
+      <c r="L34" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="M34" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="N34" t="s">
         <v>97</v>
@@ -3068,14 +3511,17 @@
       <c r="I35" t="s">
         <v>70</v>
       </c>
+      <c r="J35" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K35" s="6">
         <v>18604743099</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N35" t="s">
         <v>97</v>
@@ -3112,14 +3558,17 @@
       <c r="I36" t="s">
         <v>70</v>
       </c>
+      <c r="J36" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K36" s="6">
         <v>18604743099</v>
       </c>
-      <c r="L36" s="9" t="s">
-        <v>153</v>
+      <c r="L36" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="M36" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N36" t="s">
         <v>97</v>
@@ -3156,14 +3605,17 @@
       <c r="I37" t="s">
         <v>70</v>
       </c>
+      <c r="J37" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K37" s="6">
         <v>18604743099</v>
       </c>
-      <c r="L37" s="8" t="s">
-        <v>136</v>
+      <c r="L37" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="M37" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N37" t="s">
         <v>97</v>
@@ -3200,14 +3652,17 @@
       <c r="I38" t="s">
         <v>70</v>
       </c>
+      <c r="J38" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K38" s="6">
         <v>18604743099</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M38" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N38" t="s">
         <v>97</v>
@@ -3244,14 +3699,17 @@
       <c r="I39" t="s">
         <v>70</v>
       </c>
+      <c r="J39" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K39" s="6">
         <v>18604743099</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M39" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N39" t="s">
         <v>97</v>
@@ -3288,14 +3746,17 @@
       <c r="I40" t="s">
         <v>70</v>
       </c>
+      <c r="J40" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K40" s="6">
         <v>18604743099</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M40" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="N40" t="s">
         <v>97</v>
@@ -3332,14 +3793,17 @@
       <c r="I41" t="s">
         <v>70</v>
       </c>
+      <c r="J41" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K41" s="6">
         <v>18604743099</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M41" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="N41" t="s">
         <v>97</v>
@@ -3376,14 +3840,17 @@
       <c r="I42" t="s">
         <v>70</v>
       </c>
+      <c r="J42" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K42" s="6">
         <v>18604743099</v>
       </c>
-      <c r="L42" s="9" t="s">
-        <v>146</v>
+      <c r="L42" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="M42" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N42" t="s">
         <v>97</v>
@@ -3409,10 +3876,10 @@
         <v>132</v>
       </c>
       <c r="F43" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="G43" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H43" t="s">
         <v>95</v>
@@ -3420,14 +3887,17 @@
       <c r="I43" t="s">
         <v>70</v>
       </c>
+      <c r="J43" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K43" s="6">
         <v>18604743099</v>
       </c>
-      <c r="L43" s="8" t="s">
-        <v>157</v>
+      <c r="L43" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="M43" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N43" t="s">
         <v>97</v>
@@ -3464,14 +3934,17 @@
       <c r="I44" t="s">
         <v>70</v>
       </c>
+      <c r="J44" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K44" s="6">
         <v>18604743099</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M44" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N44" t="s">
         <v>97</v>
@@ -3508,14 +3981,17 @@
       <c r="I45" t="s">
         <v>70</v>
       </c>
+      <c r="J45" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K45" s="6">
         <v>18604743099</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N45" t="s">
         <v>97</v>
@@ -3552,14 +4028,17 @@
       <c r="I46" t="s">
         <v>70</v>
       </c>
+      <c r="J46" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K46" s="6">
         <v>18604743099</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="M46" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N46" t="s">
         <v>97</v>
@@ -3596,14 +4075,17 @@
       <c r="I47" t="s">
         <v>70</v>
       </c>
+      <c r="J47" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K47" s="6">
         <v>18604743099</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="M47" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N47" t="s">
         <v>97</v>
@@ -3640,14 +4122,17 @@
       <c r="I48" t="s">
         <v>70</v>
       </c>
+      <c r="J48" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K48" s="6">
         <v>18604743099</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="M48" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N48" t="s">
         <v>97</v>
@@ -3684,14 +4169,17 @@
       <c r="I49" t="s">
         <v>70</v>
       </c>
+      <c r="J49" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K49" s="6">
         <v>18604743099</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M49" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N49" t="s">
         <v>97</v>
@@ -3717,10 +4205,10 @@
         <v>132</v>
       </c>
       <c r="F50" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="H50" t="s">
         <v>95</v>
@@ -3728,14 +4216,17 @@
       <c r="I50" t="s">
         <v>70</v>
       </c>
+      <c r="J50" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K50" s="6">
         <v>18604743099</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="M50" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="N50" t="s">
         <v>97</v>
@@ -3772,14 +4263,17 @@
       <c r="I51" t="s">
         <v>70</v>
       </c>
+      <c r="J51" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K51" s="6">
         <v>18604743099</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M51" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N51" t="s">
         <v>97</v>
@@ -3816,14 +4310,17 @@
       <c r="I52" t="s">
         <v>70</v>
       </c>
+      <c r="J52" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K52" s="6">
         <v>18604743099</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M52" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="N52" t="s">
         <v>97</v>
@@ -3849,10 +4346,10 @@
         <v>132</v>
       </c>
       <c r="F53" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G53" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H53" t="s">
         <v>95</v>
@@ -3860,14 +4357,17 @@
       <c r="I53" t="s">
         <v>70</v>
       </c>
+      <c r="J53" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K53" s="6">
         <v>18604743099</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M53" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="N53" t="s">
         <v>97</v>
@@ -3904,14 +4404,17 @@
       <c r="I54" t="s">
         <v>70</v>
       </c>
+      <c r="J54" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K54" s="6">
         <v>18604743099</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N54" t="s">
         <v>97</v>
@@ -3948,14 +4451,17 @@
       <c r="I55" t="s">
         <v>70</v>
       </c>
+      <c r="J55" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K55" s="6">
         <v>18604743099</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N55" t="s">
         <v>97</v>
@@ -3992,14 +4498,17 @@
       <c r="I56" t="s">
         <v>70</v>
       </c>
+      <c r="J56" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K56" s="6">
         <v>18604743099</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M56" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N56" t="s">
         <v>97</v>
@@ -4036,14 +4545,17 @@
       <c r="I57" t="s">
         <v>70</v>
       </c>
+      <c r="J57" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K57" s="6">
         <v>18604743099</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M57" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N57" t="s">
         <v>97</v>
@@ -4080,14 +4592,17 @@
       <c r="I58" t="s">
         <v>70</v>
       </c>
+      <c r="J58" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K58" s="6">
         <v>18604743099</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N58" t="s">
         <v>97</v>
@@ -4124,14 +4639,17 @@
       <c r="I59" t="s">
         <v>70</v>
       </c>
+      <c r="J59" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K59" s="6">
         <v>18604743099</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M59" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N59" t="s">
         <v>97</v>
@@ -4168,14 +4686,17 @@
       <c r="I60" t="s">
         <v>70</v>
       </c>
+      <c r="J60" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K60" s="6">
         <v>18604743099</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M60" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N60" t="s">
         <v>97</v>
@@ -4212,14 +4733,17 @@
       <c r="I61" t="s">
         <v>70</v>
       </c>
+      <c r="J61" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K61" s="6">
         <v>18604743099</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M61" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N61" t="s">
         <v>97</v>
@@ -4256,14 +4780,17 @@
       <c r="I62" t="s">
         <v>70</v>
       </c>
+      <c r="J62" s="10" t="s">
+        <v>353</v>
+      </c>
       <c r="K62" s="6">
         <v>18604743099</v>
       </c>
       <c r="L62" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M62" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N62" t="s">
         <v>97</v>
@@ -4274,40 +4801,43 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C63">
-        <v>109.86819300000001</v>
+        <v>113.117768</v>
       </c>
       <c r="D63">
-        <v>39.495933000000001</v>
+        <v>41.084122000000001</v>
       </c>
       <c r="E63" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="F63" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="G63" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="H63" t="s">
         <v>95</v>
       </c>
       <c r="I63" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>353</v>
       </c>
       <c r="K63" s="6">
-        <v>13312341234</v>
+        <v>18604743099</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M63" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N63" t="s">
         <v>97</v>
@@ -4344,14 +4874,17 @@
       <c r="I64" t="s">
         <v>66</v>
       </c>
+      <c r="J64" t="s">
+        <v>354</v>
+      </c>
       <c r="K64" s="6">
         <v>13312341234</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M64" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N64" t="s">
         <v>97</v>
@@ -4388,14 +4921,17 @@
       <c r="I65" t="s">
         <v>66</v>
       </c>
+      <c r="J65" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K65" s="6">
         <v>13312341234</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N65" t="s">
         <v>97</v>
@@ -4432,14 +4968,17 @@
       <c r="I66" t="s">
         <v>66</v>
       </c>
+      <c r="J66" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K66" s="6">
         <v>13312341234</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M66" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N66" t="s">
         <v>97</v>
@@ -4476,14 +5015,17 @@
       <c r="I67" t="s">
         <v>66</v>
       </c>
+      <c r="J67" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K67" s="6">
         <v>13312341234</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M67" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N67" t="s">
         <v>97</v>
@@ -4520,14 +5062,17 @@
       <c r="I68" t="s">
         <v>66</v>
       </c>
+      <c r="J68" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K68" s="6">
         <v>13312341234</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M68" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N68" t="s">
         <v>97</v>
@@ -4564,14 +5109,17 @@
       <c r="I69" t="s">
         <v>66</v>
       </c>
+      <c r="J69" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K69" s="6">
         <v>13312341234</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M69" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N69" t="s">
         <v>97</v>
@@ -4597,10 +5145,10 @@
         <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="G70" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="H70" t="s">
         <v>95</v>
@@ -4608,14 +5156,17 @@
       <c r="I70" t="s">
         <v>66</v>
       </c>
+      <c r="J70" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K70" s="6">
         <v>13312341234</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M70" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="N70" t="s">
         <v>97</v>
@@ -4652,14 +5203,17 @@
       <c r="I71" t="s">
         <v>66</v>
       </c>
+      <c r="J71" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K71" s="6">
         <v>13312341234</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M71" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N71" t="s">
         <v>97</v>
@@ -4696,14 +5250,17 @@
       <c r="I72" t="s">
         <v>66</v>
       </c>
+      <c r="J72" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K72" s="6">
         <v>13312341234</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M72" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="N72" t="s">
         <v>97</v>
@@ -4729,10 +5286,10 @@
         <v>178</v>
       </c>
       <c r="F73" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G73" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H73" t="s">
         <v>95</v>
@@ -4740,14 +5297,17 @@
       <c r="I73" t="s">
         <v>66</v>
       </c>
+      <c r="J73" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K73" s="6">
         <v>13312341234</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M73" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="N73" t="s">
         <v>97</v>
@@ -4784,14 +5344,17 @@
       <c r="I74" t="s">
         <v>66</v>
       </c>
+      <c r="J74" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K74" s="6">
         <v>13312341234</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M74" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N74" t="s">
         <v>97</v>
@@ -4828,14 +5391,17 @@
       <c r="I75" t="s">
         <v>66</v>
       </c>
+      <c r="J75" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K75" s="6">
         <v>13312341234</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M75" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N75" t="s">
         <v>97</v>
@@ -4872,14 +5438,17 @@
       <c r="I76" t="s">
         <v>66</v>
       </c>
+      <c r="J76" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K76" s="6">
         <v>13312341234</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M76" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N76" t="s">
         <v>97</v>
@@ -4916,14 +5485,17 @@
       <c r="I77" t="s">
         <v>66</v>
       </c>
+      <c r="J77" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K77" s="6">
         <v>13312341234</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M77" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N77" t="s">
         <v>97</v>
@@ -4960,14 +5532,17 @@
       <c r="I78" t="s">
         <v>66</v>
       </c>
+      <c r="J78" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K78" s="6">
         <v>13312341234</v>
       </c>
       <c r="L78" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N78" t="s">
         <v>97</v>
@@ -5004,14 +5579,17 @@
       <c r="I79" t="s">
         <v>66</v>
       </c>
+      <c r="J79" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K79" s="6">
         <v>13312341234</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M79" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N79" t="s">
         <v>97</v>
@@ -5048,14 +5626,17 @@
       <c r="I80" t="s">
         <v>66</v>
       </c>
+      <c r="J80" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K80" s="6">
         <v>13312341234</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M80" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N80" t="s">
         <v>97</v>
@@ -5092,14 +5673,17 @@
       <c r="I81" t="s">
         <v>66</v>
       </c>
+      <c r="J81" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K81" s="6">
         <v>13312341234</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M81" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N81" t="s">
         <v>97</v>
@@ -5136,14 +5720,17 @@
       <c r="I82" t="s">
         <v>66</v>
       </c>
+      <c r="J82" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K82" s="6">
         <v>13312341234</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M82" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N82" t="s">
         <v>97</v>
@@ -5169,10 +5756,10 @@
         <v>178</v>
       </c>
       <c r="F83" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="G83" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="H83" t="s">
         <v>95</v>
@@ -5180,14 +5767,17 @@
       <c r="I83" t="s">
         <v>66</v>
       </c>
+      <c r="J83" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K83" s="6">
         <v>13312341234</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N83" t="s">
         <v>97</v>
@@ -5224,14 +5814,17 @@
       <c r="I84" t="s">
         <v>66</v>
       </c>
+      <c r="J84" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K84" s="6">
         <v>13312341234</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N84" t="s">
         <v>97</v>
@@ -5268,14 +5861,17 @@
       <c r="I85" t="s">
         <v>66</v>
       </c>
+      <c r="J85" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K85" s="6">
         <v>13312341234</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M85" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N85" t="s">
         <v>97</v>
@@ -5312,14 +5908,17 @@
       <c r="I86" t="s">
         <v>66</v>
       </c>
+      <c r="J86" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K86" s="6">
         <v>13312341234</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M86" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N86" t="s">
         <v>97</v>
@@ -5356,14 +5955,17 @@
       <c r="I87" t="s">
         <v>66</v>
       </c>
+      <c r="J87" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K87" s="6">
         <v>13312341234</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M87" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N87" t="s">
         <v>97</v>
@@ -5400,14 +6002,17 @@
       <c r="I88" t="s">
         <v>66</v>
       </c>
+      <c r="J88" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K88" s="6">
         <v>13312341234</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M88" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N88" t="s">
         <v>97</v>
@@ -5444,14 +6049,17 @@
       <c r="I89" t="s">
         <v>66</v>
       </c>
+      <c r="J89" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K89" s="6">
         <v>13312341234</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N89" t="s">
         <v>97</v>
@@ -5488,14 +6096,17 @@
       <c r="I90" t="s">
         <v>66</v>
       </c>
+      <c r="J90" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K90" s="6">
         <v>13312341234</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M90" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="N90" t="s">
         <v>97</v>
@@ -5532,14 +6143,17 @@
       <c r="I91" t="s">
         <v>66</v>
       </c>
+      <c r="J91" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K91" s="6">
         <v>13312341234</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M91" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N91" t="s">
         <v>97</v>
@@ -5576,14 +6190,17 @@
       <c r="I92" t="s">
         <v>66</v>
       </c>
+      <c r="J92" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K92" s="6">
         <v>13312341234</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M92" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N92" t="s">
         <v>97</v>
@@ -5620,14 +6237,17 @@
       <c r="I93" t="s">
         <v>66</v>
       </c>
+      <c r="J93" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K93" s="6">
         <v>13312341234</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M93" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N93" t="s">
         <v>97</v>
@@ -5664,14 +6284,17 @@
       <c r="I94" t="s">
         <v>66</v>
       </c>
+      <c r="J94" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K94" s="6">
         <v>13312341234</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M94" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="N94" t="s">
         <v>97</v>
@@ -5708,14 +6331,17 @@
       <c r="I95" t="s">
         <v>66</v>
       </c>
+      <c r="J95" s="10" t="s">
+        <v>354</v>
+      </c>
       <c r="K95" s="6">
         <v>13312341234</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M95" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N95" t="s">
         <v>97</v>
@@ -5726,40 +6352,43 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>334</v>
+        <v>177</v>
       </c>
       <c r="C96">
-        <v>100.997513</v>
+        <v>109.86819300000001</v>
       </c>
       <c r="D96">
-        <v>42.012017</v>
+        <v>39.495933000000001</v>
       </c>
       <c r="E96" t="s">
-        <v>302</v>
+        <v>178</v>
       </c>
       <c r="F96" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G96" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="H96" t="s">
         <v>95</v>
       </c>
       <c r="I96" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="J96" s="10" t="s">
+        <v>354</v>
       </c>
       <c r="K96" s="6">
-        <v>17760578425</v>
-      </c>
-      <c r="L96" s="9" t="s">
-        <v>303</v>
+        <v>13312341234</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>215</v>
       </c>
       <c r="M96" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="N96" t="s">
         <v>97</v>
@@ -5782,7 +6411,7 @@
         <v>42.012017</v>
       </c>
       <c r="E97" t="s">
-        <v>217</v>
+        <v>302</v>
       </c>
       <c r="F97" t="s">
         <v>115</v>
@@ -5796,14 +6425,17 @@
       <c r="I97" t="s">
         <v>72</v>
       </c>
+      <c r="J97" t="s">
+        <v>355</v>
+      </c>
       <c r="K97" s="6">
         <v>17760578425</v>
       </c>
-      <c r="L97" s="8" t="s">
-        <v>304</v>
+      <c r="L97" s="9" t="s">
+        <v>303</v>
       </c>
       <c r="M97" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N97" t="s">
         <v>97</v>
@@ -5840,14 +6472,17 @@
       <c r="I98" t="s">
         <v>72</v>
       </c>
+      <c r="J98" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K98" s="6">
         <v>17760578425</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M98" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="N98" t="s">
         <v>97</v>
@@ -5873,10 +6508,10 @@
         <v>217</v>
       </c>
       <c r="F99" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G99" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H99" t="s">
         <v>95</v>
@@ -5884,14 +6519,17 @@
       <c r="I99" t="s">
         <v>72</v>
       </c>
+      <c r="J99" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K99" s="6">
         <v>17760578425</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M99" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="N99" t="s">
         <v>97</v>
@@ -5928,14 +6566,17 @@
       <c r="I100" t="s">
         <v>72</v>
       </c>
+      <c r="J100" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K100" s="6">
         <v>17760578425</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M100" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N100" t="s">
         <v>97</v>
@@ -5972,14 +6613,17 @@
       <c r="I101" t="s">
         <v>72</v>
       </c>
+      <c r="J101" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K101" s="6">
         <v>17760578425</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M101" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N101" t="s">
         <v>97</v>
@@ -6016,14 +6660,17 @@
       <c r="I102" t="s">
         <v>72</v>
       </c>
+      <c r="J102" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K102" s="6">
         <v>17760578425</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M102" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N102" t="s">
         <v>97</v>
@@ -6060,14 +6707,17 @@
       <c r="I103" t="s">
         <v>72</v>
       </c>
+      <c r="J103" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K103" s="6">
         <v>17760578425</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M103" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N103" t="s">
         <v>97</v>
@@ -6104,14 +6754,17 @@
       <c r="I104" t="s">
         <v>72</v>
       </c>
+      <c r="J104" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K104" s="6">
         <v>17760578425</v>
       </c>
       <c r="L104" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M104" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N104" t="s">
         <v>97</v>
@@ -6148,14 +6801,17 @@
       <c r="I105" t="s">
         <v>72</v>
       </c>
+      <c r="J105" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K105" s="6">
         <v>17760578425</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M105" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N105" t="s">
         <v>97</v>
@@ -6192,14 +6848,17 @@
       <c r="I106" t="s">
         <v>72</v>
       </c>
+      <c r="J106" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K106" s="6">
         <v>17760578425</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M106" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N106" t="s">
         <v>97</v>
@@ -6236,14 +6895,17 @@
       <c r="I107" t="s">
         <v>72</v>
       </c>
+      <c r="J107" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K107" s="6">
         <v>17760578425</v>
       </c>
       <c r="L107" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M107" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N107" t="s">
         <v>97</v>
@@ -6280,14 +6942,17 @@
       <c r="I108" t="s">
         <v>72</v>
       </c>
+      <c r="J108" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K108" s="6">
         <v>17760578425</v>
       </c>
       <c r="L108" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M108" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N108" t="s">
         <v>97</v>
@@ -6313,10 +6978,10 @@
         <v>217</v>
       </c>
       <c r="F109" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="G109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H109" t="s">
         <v>95</v>
@@ -6324,14 +6989,17 @@
       <c r="I109" t="s">
         <v>72</v>
       </c>
+      <c r="J109" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K109" s="6">
         <v>17760578425</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M109" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N109" t="s">
         <v>97</v>
@@ -6368,14 +7036,17 @@
       <c r="I110" t="s">
         <v>72</v>
       </c>
+      <c r="J110" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K110" s="6">
         <v>17760578425</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M110" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N110" t="s">
         <v>97</v>
@@ -6412,14 +7083,17 @@
       <c r="I111" t="s">
         <v>72</v>
       </c>
+      <c r="J111" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K111" s="6">
         <v>17760578425</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M111" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N111" t="s">
         <v>97</v>
@@ -6456,14 +7130,17 @@
       <c r="I112" t="s">
         <v>72</v>
       </c>
+      <c r="J112" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K112" s="6">
         <v>17760578425</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M112" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N112" t="s">
         <v>97</v>
@@ -6500,14 +7177,17 @@
       <c r="I113" t="s">
         <v>72</v>
       </c>
+      <c r="J113" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K113" s="6">
         <v>17760578425</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M113" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N113" t="s">
         <v>97</v>
@@ -6544,14 +7224,17 @@
       <c r="I114" t="s">
         <v>72</v>
       </c>
+      <c r="J114" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K114" s="6">
         <v>17760578425</v>
       </c>
       <c r="L114" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M114" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N114" t="s">
         <v>97</v>
@@ -6588,14 +7271,17 @@
       <c r="I115" t="s">
         <v>72</v>
       </c>
+      <c r="J115" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K115" s="6">
         <v>17760578425</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M115" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N115" t="s">
         <v>97</v>
@@ -6621,10 +7307,10 @@
         <v>217</v>
       </c>
       <c r="F116" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="G116" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H116" t="s">
         <v>95</v>
@@ -6632,14 +7318,17 @@
       <c r="I116" t="s">
         <v>72</v>
       </c>
+      <c r="J116" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K116" s="6">
         <v>17760578425</v>
       </c>
       <c r="L116" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N116" t="s">
         <v>97</v>
@@ -6676,14 +7365,17 @@
       <c r="I117" t="s">
         <v>72</v>
       </c>
+      <c r="J117" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K117" s="6">
         <v>17760578425</v>
       </c>
       <c r="L117" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M117" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N117" t="s">
         <v>97</v>
@@ -6720,14 +7412,17 @@
       <c r="I118" t="s">
         <v>72</v>
       </c>
+      <c r="J118" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K118" s="6">
         <v>17760578425</v>
       </c>
       <c r="L118" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M118" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N118" t="s">
         <v>97</v>
@@ -6764,14 +7459,17 @@
       <c r="I119" t="s">
         <v>72</v>
       </c>
+      <c r="J119" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K119" s="6">
         <v>17760578425</v>
       </c>
       <c r="L119" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M119" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N119" t="s">
         <v>97</v>
@@ -6808,14 +7506,17 @@
       <c r="I120" t="s">
         <v>72</v>
       </c>
+      <c r="J120" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K120" s="6">
         <v>17760578425</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M120" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N120" t="s">
         <v>97</v>
@@ -6852,14 +7553,17 @@
       <c r="I121" t="s">
         <v>72</v>
       </c>
+      <c r="J121" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K121" s="6">
         <v>17760578425</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M121" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N121" t="s">
         <v>97</v>
@@ -6896,14 +7600,17 @@
       <c r="I122" t="s">
         <v>72</v>
       </c>
+      <c r="J122" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K122" s="6">
         <v>17760578425</v>
       </c>
       <c r="L122" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M122" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N122" t="s">
         <v>97</v>
@@ -6940,14 +7647,17 @@
       <c r="I123" t="s">
         <v>72</v>
       </c>
+      <c r="J123" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K123" s="6">
         <v>17760578425</v>
       </c>
       <c r="L123" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M123" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="N123" t="s">
         <v>97</v>
@@ -6984,14 +7694,17 @@
       <c r="I124" t="s">
         <v>72</v>
       </c>
+      <c r="J124" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K124" s="6">
         <v>17760578425</v>
       </c>
-      <c r="L124" s="9" t="s">
-        <v>336</v>
+      <c r="L124" s="8" t="s">
+        <v>330</v>
       </c>
       <c r="M124" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N124" t="s">
         <v>97</v>
@@ -7028,14 +7741,17 @@
       <c r="I125" t="s">
         <v>72</v>
       </c>
+      <c r="J125" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K125" s="6">
         <v>17760578425</v>
       </c>
-      <c r="L125" s="8" t="s">
-        <v>331</v>
+      <c r="L125" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="M125" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N125" t="s">
         <v>97</v>
@@ -7072,14 +7788,17 @@
       <c r="I126" t="s">
         <v>72</v>
       </c>
+      <c r="J126" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K126" s="6">
         <v>17760578425</v>
       </c>
-      <c r="L126" s="9" t="s">
-        <v>335</v>
+      <c r="L126" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="M126" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N126" t="s">
         <v>97</v>
@@ -7116,14 +7835,17 @@
       <c r="I127" t="s">
         <v>72</v>
       </c>
+      <c r="J127" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K127" s="6">
         <v>17760578425</v>
       </c>
-      <c r="L127" s="8" t="s">
-        <v>332</v>
+      <c r="L127" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="M127" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="N127" t="s">
         <v>97</v>
@@ -7160,14 +7882,17 @@
       <c r="I128" t="s">
         <v>72</v>
       </c>
+      <c r="J128" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K128" s="6">
         <v>17760578425</v>
       </c>
       <c r="L128" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M128" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N128" t="s">
         <v>97</v>
@@ -7178,40 +7903,43 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>223</v>
+        <v>334</v>
       </c>
       <c r="C129">
-        <v>107.739835</v>
+        <v>100.997513</v>
       </c>
       <c r="D129">
-        <v>40.922080000000001</v>
+        <v>42.012017</v>
       </c>
       <c r="E129" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F129" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G129" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H129" t="s">
         <v>95</v>
       </c>
       <c r="I129" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="J129" s="10" t="s">
+        <v>355</v>
       </c>
       <c r="K129" s="6">
-        <v>18004788111</v>
+        <v>17760578425</v>
       </c>
       <c r="L129" s="8" t="s">
-        <v>226</v>
+        <v>333</v>
       </c>
       <c r="M129" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="N129" t="s">
         <v>97</v>
@@ -7248,14 +7976,17 @@
       <c r="I130" t="s">
         <v>71</v>
       </c>
+      <c r="J130" t="s">
+        <v>356</v>
+      </c>
       <c r="K130" s="6">
         <v>18004788111</v>
       </c>
       <c r="L130" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M130" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N130" t="s">
         <v>97</v>
@@ -7292,14 +8023,17 @@
       <c r="I131" t="s">
         <v>71</v>
       </c>
+      <c r="J131" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K131" s="6">
         <v>18004788111</v>
       </c>
       <c r="L131" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M131" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="N131" t="s">
         <v>97</v>
@@ -7325,10 +8059,10 @@
         <v>224</v>
       </c>
       <c r="F132" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G132" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H132" t="s">
         <v>95</v>
@@ -7336,14 +8070,17 @@
       <c r="I132" t="s">
         <v>71</v>
       </c>
+      <c r="J132" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K132" s="6">
         <v>18004788111</v>
       </c>
       <c r="L132" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M132" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="N132" t="s">
         <v>97</v>
@@ -7380,14 +8117,17 @@
       <c r="I133" t="s">
         <v>71</v>
       </c>
+      <c r="J133" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K133" s="6">
         <v>18004788111</v>
       </c>
       <c r="L133" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M133" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N133" t="s">
         <v>97</v>
@@ -7424,14 +8164,17 @@
       <c r="I134" t="s">
         <v>71</v>
       </c>
+      <c r="J134" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K134" s="6">
         <v>18004788111</v>
       </c>
       <c r="L134" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M134" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N134" t="s">
         <v>97</v>
@@ -7468,14 +8211,17 @@
       <c r="I135" t="s">
         <v>71</v>
       </c>
+      <c r="J135" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K135" s="6">
         <v>18004788111</v>
       </c>
       <c r="L135" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M135" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N135" t="s">
         <v>97</v>
@@ -7512,14 +8258,17 @@
       <c r="I136" t="s">
         <v>71</v>
       </c>
+      <c r="J136" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K136" s="6">
         <v>18004788111</v>
       </c>
       <c r="L136" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M136" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N136" t="s">
         <v>97</v>
@@ -7556,14 +8305,17 @@
       <c r="I137" t="s">
         <v>71</v>
       </c>
+      <c r="J137" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K137" s="6">
         <v>18004788111</v>
       </c>
       <c r="L137" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M137" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N137" t="s">
         <v>97</v>
@@ -7600,14 +8352,17 @@
       <c r="I138" t="s">
         <v>71</v>
       </c>
+      <c r="J138" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K138" s="6">
         <v>18004788111</v>
       </c>
       <c r="L138" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M138" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N138" t="s">
         <v>97</v>
@@ -7644,14 +8399,17 @@
       <c r="I139" t="s">
         <v>71</v>
       </c>
+      <c r="J139" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K139" s="6">
         <v>18004788111</v>
       </c>
       <c r="L139" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M139" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="N139" t="s">
         <v>97</v>
@@ -7688,14 +8446,17 @@
       <c r="I140" t="s">
         <v>71</v>
       </c>
+      <c r="J140" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K140" s="6">
         <v>18004788111</v>
       </c>
       <c r="L140" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M140" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N140" t="s">
         <v>97</v>
@@ -7732,14 +8493,17 @@
       <c r="I141" t="s">
         <v>71</v>
       </c>
+      <c r="J141" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K141" s="6">
         <v>18004788111</v>
       </c>
       <c r="L141" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M141" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N141" t="s">
         <v>97</v>
@@ -7776,14 +8540,17 @@
       <c r="I142" t="s">
         <v>71</v>
       </c>
+      <c r="J142" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K142" s="6">
         <v>18004788111</v>
       </c>
       <c r="L142" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M142" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N142" t="s">
         <v>97</v>
@@ -7820,14 +8587,17 @@
       <c r="I143" t="s">
         <v>71</v>
       </c>
+      <c r="J143" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K143" s="6">
         <v>18004788111</v>
       </c>
       <c r="L143" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M143" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="N143" t="s">
         <v>97</v>
@@ -7864,14 +8634,17 @@
       <c r="I144" t="s">
         <v>71</v>
       </c>
+      <c r="J144" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K144" s="6">
         <v>18004788111</v>
       </c>
       <c r="L144" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M144" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N144" t="s">
         <v>97</v>
@@ -7897,10 +8670,10 @@
         <v>224</v>
       </c>
       <c r="F145" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="G145" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="H145" t="s">
         <v>95</v>
@@ -7908,14 +8681,17 @@
       <c r="I145" t="s">
         <v>71</v>
       </c>
+      <c r="J145" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K145" s="6">
         <v>18004788111</v>
       </c>
       <c r="L145" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N145" t="s">
         <v>97</v>
@@ -7952,14 +8728,17 @@
       <c r="I146" t="s">
         <v>71</v>
       </c>
+      <c r="J146" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K146" s="6">
         <v>18004788111</v>
       </c>
       <c r="L146" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M146" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N146" t="s">
         <v>97</v>
@@ -7996,14 +8775,17 @@
       <c r="I147" t="s">
         <v>71</v>
       </c>
+      <c r="J147" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K147" s="6">
         <v>18004788111</v>
       </c>
       <c r="L147" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M147" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N147" t="s">
         <v>97</v>
@@ -8040,14 +8822,17 @@
       <c r="I148" t="s">
         <v>71</v>
       </c>
+      <c r="J148" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K148" s="6">
         <v>18004788111</v>
       </c>
       <c r="L148" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M148" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N148" t="s">
         <v>97</v>
@@ -8084,14 +8869,17 @@
       <c r="I149" t="s">
         <v>71</v>
       </c>
+      <c r="J149" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K149" s="6">
         <v>18004788111</v>
       </c>
       <c r="L149" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M149" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N149" t="s">
         <v>97</v>
@@ -8128,14 +8916,17 @@
       <c r="I150" t="s">
         <v>71</v>
       </c>
+      <c r="J150" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K150" s="6">
         <v>18004788111</v>
       </c>
       <c r="L150" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M150" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N150" t="s">
         <v>97</v>
@@ -8172,14 +8963,17 @@
       <c r="I151" t="s">
         <v>71</v>
       </c>
+      <c r="J151" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K151" s="6">
         <v>18004788111</v>
       </c>
       <c r="L151" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M151" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N151" t="s">
         <v>97</v>
@@ -8216,14 +9010,17 @@
       <c r="I152" t="s">
         <v>71</v>
       </c>
+      <c r="J152" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K152" s="6">
         <v>18004788111</v>
       </c>
       <c r="L152" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M152" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N152" t="s">
         <v>97</v>
@@ -8260,14 +9057,17 @@
       <c r="I153" t="s">
         <v>71</v>
       </c>
+      <c r="J153" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K153" s="6">
         <v>18004788111</v>
       </c>
       <c r="L153" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M153" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N153" t="s">
         <v>97</v>
@@ -8304,14 +9104,17 @@
       <c r="I154" t="s">
         <v>71</v>
       </c>
+      <c r="J154" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K154" s="6">
         <v>18004788111</v>
       </c>
       <c r="L154" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M154" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N154" t="s">
         <v>97</v>
@@ -8337,10 +9140,10 @@
         <v>224</v>
       </c>
       <c r="F155" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="G155" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H155" t="s">
         <v>95</v>
@@ -8348,14 +9151,17 @@
       <c r="I155" t="s">
         <v>71</v>
       </c>
+      <c r="J155" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K155" s="6">
         <v>18004788111</v>
       </c>
       <c r="L155" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M155" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N155" t="s">
         <v>97</v>
@@ -8392,14 +9198,17 @@
       <c r="I156" t="s">
         <v>71</v>
       </c>
+      <c r="J156" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K156" s="6">
         <v>18004788111</v>
       </c>
       <c r="L156" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M156" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N156" t="s">
         <v>97</v>
@@ -8436,14 +9245,17 @@
       <c r="I157" t="s">
         <v>71</v>
       </c>
+      <c r="J157" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K157" s="6">
         <v>18004788111</v>
       </c>
       <c r="L157" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M157" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N157" t="s">
         <v>97</v>
@@ -8480,14 +9292,17 @@
       <c r="I158" t="s">
         <v>71</v>
       </c>
+      <c r="J158" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K158" s="6">
         <v>18004788111</v>
       </c>
       <c r="L158" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M158" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N158" t="s">
         <v>97</v>
@@ -8524,14 +9339,17 @@
       <c r="I159" t="s">
         <v>71</v>
       </c>
+      <c r="J159" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K159" s="6">
         <v>18004788111</v>
       </c>
       <c r="L159" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M159" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N159" t="s">
         <v>97</v>
@@ -8568,14 +9386,17 @@
       <c r="I160" t="s">
         <v>71</v>
       </c>
+      <c r="J160" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K160" s="6">
         <v>18004788111</v>
       </c>
       <c r="L160" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M160" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N160" t="s">
         <v>97</v>
@@ -8612,14 +9433,17 @@
       <c r="I161" t="s">
         <v>71</v>
       </c>
+      <c r="J161" s="10" t="s">
+        <v>356</v>
+      </c>
       <c r="K161" s="6">
         <v>18004788111</v>
       </c>
       <c r="L161" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M161" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N161" t="s">
         <v>97</v>
@@ -8630,40 +9454,43 @@
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>262</v>
+        <v>222</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="C162">
-        <v>101.54625</v>
+        <v>107.739835</v>
       </c>
       <c r="D162">
-        <v>39.223269999999999</v>
+        <v>40.922080000000001</v>
       </c>
       <c r="E162" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="F162" t="s">
         <v>93</v>
       </c>
       <c r="G162" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="H162" t="s">
         <v>95</v>
       </c>
       <c r="I162" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="J162" s="10" t="s">
+        <v>356</v>
       </c>
       <c r="K162" s="6">
-        <v>17760578425</v>
-      </c>
-      <c r="L162" s="7" t="s">
-        <v>266</v>
+        <v>18004788111</v>
+      </c>
+      <c r="L162" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="M162" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N162" t="s">
         <v>97</v>
@@ -8700,14 +9527,17 @@
       <c r="I163" t="s">
         <v>72</v>
       </c>
+      <c r="J163" t="s">
+        <v>355</v>
+      </c>
       <c r="K163" s="6">
         <v>17760578425</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M163" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N163" t="s">
         <v>97</v>
@@ -8744,14 +9574,17 @@
       <c r="I164" t="s">
         <v>72</v>
       </c>
+      <c r="J164" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K164" s="6">
         <v>17760578425</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M164" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N164" t="s">
         <v>97</v>
@@ -8788,14 +9621,17 @@
       <c r="I165" t="s">
         <v>72</v>
       </c>
+      <c r="J165" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K165" s="6">
         <v>17760578425</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M165" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N165" t="s">
         <v>97</v>
@@ -8832,14 +9668,17 @@
       <c r="I166" t="s">
         <v>72</v>
       </c>
+      <c r="J166" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K166" s="6">
         <v>17760578425</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M166" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N166" t="s">
         <v>97</v>
@@ -8876,14 +9715,17 @@
       <c r="I167" t="s">
         <v>72</v>
       </c>
+      <c r="J167" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K167" s="6">
         <v>17760578425</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M167" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N167" t="s">
         <v>97</v>
@@ -8920,14 +9762,17 @@
       <c r="I168" t="s">
         <v>72</v>
       </c>
+      <c r="J168" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K168" s="6">
         <v>17760578425</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M168" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N168" t="s">
         <v>97</v>
@@ -8953,10 +9798,10 @@
         <v>264</v>
       </c>
       <c r="F169" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="G169" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="H169" t="s">
         <v>95</v>
@@ -8964,14 +9809,17 @@
       <c r="I169" t="s">
         <v>72</v>
       </c>
+      <c r="J169" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K169" s="6">
         <v>17760578425</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M169" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N169" t="s">
         <v>97</v>
@@ -9008,14 +9856,17 @@
       <c r="I170" t="s">
         <v>72</v>
       </c>
+      <c r="J170" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K170" s="6">
         <v>17760578425</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M170" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N170" t="s">
         <v>97</v>
@@ -9052,14 +9903,17 @@
       <c r="I171" t="s">
         <v>72</v>
       </c>
+      <c r="J171" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K171" s="6">
         <v>17760578425</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M171" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N171" t="s">
         <v>97</v>
@@ -9096,14 +9950,17 @@
       <c r="I172" t="s">
         <v>72</v>
       </c>
+      <c r="J172" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K172" s="6">
         <v>17760578425</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M172" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N172" t="s">
         <v>97</v>
@@ -9140,14 +9997,17 @@
       <c r="I173" t="s">
         <v>72</v>
       </c>
+      <c r="J173" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K173" s="6">
         <v>17760578425</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M173" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N173" t="s">
         <v>97</v>
@@ -9184,14 +10044,17 @@
       <c r="I174" t="s">
         <v>72</v>
       </c>
+      <c r="J174" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K174" s="6">
         <v>17760578425</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M174" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N174" t="s">
         <v>97</v>
@@ -9228,14 +10091,17 @@
       <c r="I175" t="s">
         <v>72</v>
       </c>
+      <c r="J175" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K175" s="6">
         <v>17760578425</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M175" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N175" t="s">
         <v>97</v>
@@ -9272,14 +10138,17 @@
       <c r="I176" t="s">
         <v>72</v>
       </c>
+      <c r="J176" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K176" s="6">
         <v>17760578425</v>
       </c>
       <c r="L176" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M176" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N176" t="s">
         <v>97</v>
@@ -9316,14 +10185,17 @@
       <c r="I177" t="s">
         <v>72</v>
       </c>
+      <c r="J177" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K177" s="6">
         <v>17760578425</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M177" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N177" t="s">
         <v>97</v>
@@ -9360,14 +10232,17 @@
       <c r="I178" t="s">
         <v>72</v>
       </c>
+      <c r="J178" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K178" s="6">
         <v>17760578425</v>
       </c>
       <c r="L178" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M178" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N178" t="s">
         <v>97</v>
@@ -9393,10 +10268,10 @@
         <v>264</v>
       </c>
       <c r="F179" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G179" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H179" t="s">
         <v>95</v>
@@ -9404,14 +10279,17 @@
       <c r="I179" t="s">
         <v>72</v>
       </c>
+      <c r="J179" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K179" s="6">
         <v>17760578425</v>
       </c>
       <c r="L179" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="M179" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="N179" t="s">
         <v>97</v>
@@ -9448,14 +10326,17 @@
       <c r="I180" t="s">
         <v>72</v>
       </c>
+      <c r="J180" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K180" s="6">
         <v>17760578425</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M180" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="N180" t="s">
         <v>97</v>
@@ -9492,14 +10373,17 @@
       <c r="I181" t="s">
         <v>72</v>
       </c>
+      <c r="J181" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K181" s="6">
         <v>17760578425</v>
       </c>
       <c r="L181" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M181" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="N181" t="s">
         <v>97</v>
@@ -9525,10 +10409,10 @@
         <v>264</v>
       </c>
       <c r="F182" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="G182" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="H182" t="s">
         <v>95</v>
@@ -9536,14 +10420,17 @@
       <c r="I182" t="s">
         <v>72</v>
       </c>
+      <c r="J182" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K182" s="6">
         <v>17760578425</v>
       </c>
       <c r="L182" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M182" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="N182" t="s">
         <v>97</v>
@@ -9580,14 +10467,17 @@
       <c r="I183" t="s">
         <v>72</v>
       </c>
+      <c r="J183" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K183" s="6">
         <v>17760578425</v>
       </c>
       <c r="L183" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M183" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N183" t="s">
         <v>97</v>
@@ -9624,14 +10514,17 @@
       <c r="I184" t="s">
         <v>72</v>
       </c>
+      <c r="J184" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K184" s="6">
         <v>17760578425</v>
       </c>
       <c r="L184" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M184" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N184" t="s">
         <v>97</v>
@@ -9668,14 +10561,17 @@
       <c r="I185" t="s">
         <v>72</v>
       </c>
+      <c r="J185" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K185" s="6">
         <v>17760578425</v>
       </c>
       <c r="L185" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M185" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N185" t="s">
         <v>97</v>
@@ -9712,14 +10608,17 @@
       <c r="I186" t="s">
         <v>72</v>
       </c>
+      <c r="J186" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K186" s="6">
         <v>17760578425</v>
       </c>
       <c r="L186" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M186" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="N186" t="s">
         <v>97</v>
@@ -9756,14 +10655,17 @@
       <c r="I187" t="s">
         <v>72</v>
       </c>
+      <c r="J187" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K187" s="6">
         <v>17760578425</v>
       </c>
       <c r="L187" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M187" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N187" t="s">
         <v>97</v>
@@ -9800,14 +10702,17 @@
       <c r="I188" t="s">
         <v>72</v>
       </c>
+      <c r="J188" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K188" s="6">
         <v>17760578425</v>
       </c>
       <c r="L188" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M188" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N188" t="s">
         <v>97</v>
@@ -9844,14 +10749,17 @@
       <c r="I189" t="s">
         <v>72</v>
       </c>
+      <c r="J189" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K189" s="6">
         <v>17760578425</v>
       </c>
       <c r="L189" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M189" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="N189" t="s">
         <v>97</v>
@@ -9888,14 +10796,17 @@
       <c r="I190" t="s">
         <v>72</v>
       </c>
+      <c r="J190" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K190" s="6">
         <v>17760578425</v>
       </c>
       <c r="L190" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M190" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N190" t="s">
         <v>97</v>
@@ -9932,14 +10843,17 @@
       <c r="I191" t="s">
         <v>72</v>
       </c>
+      <c r="J191" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K191" s="6">
         <v>17760578425</v>
       </c>
       <c r="L191" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M191" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N191" t="s">
         <v>97</v>
@@ -9976,14 +10890,17 @@
       <c r="I192" t="s">
         <v>72</v>
       </c>
+      <c r="J192" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K192" s="6">
         <v>17760578425</v>
       </c>
       <c r="L192" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M192" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N192" t="s">
         <v>97</v>
@@ -10020,14 +10937,17 @@
       <c r="I193" t="s">
         <v>72</v>
       </c>
+      <c r="J193" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K193" s="6">
         <v>17760578425</v>
       </c>
       <c r="L193" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M193" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="N193" t="s">
         <v>97</v>
@@ -10064,19 +10984,69 @@
       <c r="I194" t="s">
         <v>72</v>
       </c>
+      <c r="J194" s="10" t="s">
+        <v>355</v>
+      </c>
       <c r="K194" s="6">
         <v>17760578425</v>
       </c>
       <c r="L194" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="M194" t="s">
+        <v>16</v>
+      </c>
+      <c r="N194" t="s">
+        <v>97</v>
+      </c>
+      <c r="O194" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>262</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C195">
+        <v>101.54625</v>
+      </c>
+      <c r="D195">
+        <v>39.223269999999999</v>
+      </c>
+      <c r="E195" t="s">
+        <v>264</v>
+      </c>
+      <c r="F195" t="s">
+        <v>133</v>
+      </c>
+      <c r="G195" t="s">
+        <v>288</v>
+      </c>
+      <c r="H195" t="s">
+        <v>95</v>
+      </c>
+      <c r="I195" t="s">
+        <v>72</v>
+      </c>
+      <c r="J195" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K195" s="6">
+        <v>17760578425</v>
+      </c>
+      <c r="L195" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="M194" t="s">
+      <c r="M195" t="s">
         <v>11</v>
       </c>
-      <c r="N194" t="s">
-        <v>97</v>
-      </c>
-      <c r="O194" t="s">
+      <c r="N195" t="s">
+        <v>97</v>
+      </c>
+      <c r="O195" t="s">
         <v>98</v>
       </c>
     </row>
@@ -10091,49 +11061,49 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L30" r:id="rId1" xr:uid="{5AFB9FE9-AFF1-4833-924D-BE65C74FB200}"/>
-    <hyperlink ref="L29" r:id="rId2" xr:uid="{5035717F-F389-4382-B91C-4A2B50463724}"/>
-    <hyperlink ref="L28" r:id="rId3" xr:uid="{9B74D91C-1F2F-42C1-9E30-AC65772BB0D3}"/>
-    <hyperlink ref="L26" r:id="rId4" xr:uid="{051F5B83-BF2B-4ADC-AF82-2457E7D333D8}"/>
-    <hyperlink ref="L25" r:id="rId5" xr:uid="{2BF5B35D-5A51-4E57-B306-E8B773A7F439}"/>
-    <hyperlink ref="L24" r:id="rId6" xr:uid="{F070D522-9197-4C78-9872-0CFAFEF3ABDD}"/>
-    <hyperlink ref="L23" r:id="rId7" xr:uid="{AD5AAF9A-2D1E-4F4B-B031-EC426938B180}"/>
-    <hyperlink ref="L22" r:id="rId8" xr:uid="{2ECDCA54-59BB-4200-A96E-20251829DDE8}"/>
-    <hyperlink ref="L21" r:id="rId9" xr:uid="{4A62ACB9-CD44-4441-9CCB-DED9C656499D}"/>
-    <hyperlink ref="L20" r:id="rId10" xr:uid="{22E62E0D-0218-4813-BC4B-6431491A149C}"/>
-    <hyperlink ref="L19" r:id="rId11" xr:uid="{7C10C684-D884-4B97-99AC-839E82895BDB}"/>
-    <hyperlink ref="L17" r:id="rId12" xr:uid="{ED4B5FBB-0397-46FC-B8CC-C55AE52E9AC4}"/>
-    <hyperlink ref="L16" r:id="rId13" xr:uid="{DEED8E33-C52F-4655-9C50-00272FCF4FFD}"/>
-    <hyperlink ref="L15" r:id="rId14" xr:uid="{DFA8BA77-7497-454E-9CEF-C6CA0A3A7027}"/>
-    <hyperlink ref="L14" r:id="rId15" xr:uid="{4F796C34-DCEF-4477-91BA-41F332D6AA8A}"/>
-    <hyperlink ref="L13" r:id="rId16" xr:uid="{41FA6ADA-BF0F-41F7-9F52-FACA7B440C52}"/>
-    <hyperlink ref="L12" r:id="rId17" xr:uid="{858433CF-883A-4102-B2A3-45BC859D94D3}"/>
-    <hyperlink ref="L10" r:id="rId18" xr:uid="{9B0C9F24-4E47-45A2-AB74-B8CC13EAAF6E}"/>
-    <hyperlink ref="L9" r:id="rId19" xr:uid="{C16CA6A8-4738-4A95-AA68-372216C6CDB5}"/>
-    <hyperlink ref="L8" r:id="rId20" xr:uid="{8674943E-41F2-4B21-9DE1-E29B621C7734}"/>
-    <hyperlink ref="L7" r:id="rId21" xr:uid="{081455DA-B87F-47D2-AB25-BA3A635C1352}"/>
-    <hyperlink ref="L6" r:id="rId22" xr:uid="{A2837E98-DB96-420C-BDFF-7C55DBDAC86F}"/>
-    <hyperlink ref="L5" r:id="rId23" xr:uid="{5486AFF9-A316-4F6C-8C32-7BC38062E511}"/>
-    <hyperlink ref="L4" r:id="rId24" xr:uid="{D44BD7AA-8277-4C14-B1E3-AEB0BBCFE79D}"/>
-    <hyperlink ref="L3" r:id="rId25" xr:uid="{2DFBF93B-99AF-41D2-87B7-C423E5851D12}"/>
-    <hyperlink ref="L2" r:id="rId26" xr:uid="{907CDA17-31D9-4CC9-AAA2-C77E3F32DCE9}"/>
-    <hyperlink ref="L1" r:id="rId27" xr:uid="{1B021039-0959-46C0-A061-76F250D32C55}"/>
-    <hyperlink ref="L18" r:id="rId28" xr:uid="{8247FD88-1371-44C7-A601-A52FA6BD25B3}"/>
-    <hyperlink ref="L33" r:id="rId29" xr:uid="{EC6E2E4F-7CCC-4158-89E0-06F25A493D34}"/>
-    <hyperlink ref="L32" r:id="rId30" xr:uid="{0703B97E-FC86-4EF1-B6E7-4A5734C5CB7D}"/>
-    <hyperlink ref="L31" r:id="rId31" xr:uid="{5B97BFDC-E863-4BDB-B983-C5FD608CEFB4}"/>
-    <hyperlink ref="L35" r:id="rId32" xr:uid="{41D4AFBB-91CD-4EF0-AC66-0546D3D97838}"/>
-    <hyperlink ref="L34" r:id="rId33" xr:uid="{E44099FF-1B8E-4B38-9BE3-4FD191D4273B}"/>
-    <hyperlink ref="L42" r:id="rId34" xr:uid="{BC3498AF-E6E0-4A79-A360-3455B91F49EE}"/>
-    <hyperlink ref="L36" r:id="rId35" xr:uid="{598DD894-F900-419D-A3C2-A860C745B615}"/>
-    <hyperlink ref="L71" r:id="rId36" xr:uid="{CB53F702-DE69-43E5-BF2A-93044BB24552}"/>
-    <hyperlink ref="L76" r:id="rId37" xr:uid="{6769CC53-79E7-4F64-86CD-D92AFC7E20C0}"/>
-    <hyperlink ref="L99" r:id="rId38" display="http://172.16.238.64:8015/15290001120001/DGR2203/B_FScan" xr:uid="{83B19AC3-668D-425D-8422-5B36234BAD96}"/>
-    <hyperlink ref="L134" r:id="rId39" xr:uid="{8090CEBA-BEE5-4E0F-8D06-6EBA44732754}"/>
-    <hyperlink ref="L162" r:id="rId40" xr:uid="{1DA01A38-0EAA-4681-977F-A6AF35C53703}"/>
-    <hyperlink ref="L96" r:id="rId41" display="http://172.16.238.64:8015/15290001120001/EM/E_QueryDeviceInfo" xr:uid="{644FC5FD-238D-4D23-9712-2B88E6617F48}"/>
-    <hyperlink ref="L126" r:id="rId42" xr:uid="{D1793EF1-D0F0-48BA-8F15-4085256EB965}"/>
-    <hyperlink ref="L124" r:id="rId43" xr:uid="{031EA670-EA3E-4A8C-9089-CB7B41EC7E05}"/>
+    <hyperlink ref="L31" r:id="rId1" xr:uid="{5AFB9FE9-AFF1-4833-924D-BE65C74FB200}"/>
+    <hyperlink ref="L30" r:id="rId2" xr:uid="{5035717F-F389-4382-B91C-4A2B50463724}"/>
+    <hyperlink ref="L29" r:id="rId3" xr:uid="{9B74D91C-1F2F-42C1-9E30-AC65772BB0D3}"/>
+    <hyperlink ref="L27" r:id="rId4" xr:uid="{051F5B83-BF2B-4ADC-AF82-2457E7D333D8}"/>
+    <hyperlink ref="L26" r:id="rId5" xr:uid="{2BF5B35D-5A51-4E57-B306-E8B773A7F439}"/>
+    <hyperlink ref="L25" r:id="rId6" xr:uid="{F070D522-9197-4C78-9872-0CFAFEF3ABDD}"/>
+    <hyperlink ref="L24" r:id="rId7" xr:uid="{AD5AAF9A-2D1E-4F4B-B031-EC426938B180}"/>
+    <hyperlink ref="L23" r:id="rId8" xr:uid="{2ECDCA54-59BB-4200-A96E-20251829DDE8}"/>
+    <hyperlink ref="L22" r:id="rId9" xr:uid="{4A62ACB9-CD44-4441-9CCB-DED9C656499D}"/>
+    <hyperlink ref="L21" r:id="rId10" xr:uid="{22E62E0D-0218-4813-BC4B-6431491A149C}"/>
+    <hyperlink ref="L20" r:id="rId11" xr:uid="{7C10C684-D884-4B97-99AC-839E82895BDB}"/>
+    <hyperlink ref="L18" r:id="rId12" xr:uid="{ED4B5FBB-0397-46FC-B8CC-C55AE52E9AC4}"/>
+    <hyperlink ref="L17" r:id="rId13" xr:uid="{DEED8E33-C52F-4655-9C50-00272FCF4FFD}"/>
+    <hyperlink ref="L16" r:id="rId14" xr:uid="{DFA8BA77-7497-454E-9CEF-C6CA0A3A7027}"/>
+    <hyperlink ref="L15" r:id="rId15" xr:uid="{4F796C34-DCEF-4477-91BA-41F332D6AA8A}"/>
+    <hyperlink ref="L14" r:id="rId16" xr:uid="{41FA6ADA-BF0F-41F7-9F52-FACA7B440C52}"/>
+    <hyperlink ref="L13" r:id="rId17" xr:uid="{858433CF-883A-4102-B2A3-45BC859D94D3}"/>
+    <hyperlink ref="L11" r:id="rId18" xr:uid="{9B0C9F24-4E47-45A2-AB74-B8CC13EAAF6E}"/>
+    <hyperlink ref="L10" r:id="rId19" xr:uid="{C16CA6A8-4738-4A95-AA68-372216C6CDB5}"/>
+    <hyperlink ref="L9" r:id="rId20" xr:uid="{8674943E-41F2-4B21-9DE1-E29B621C7734}"/>
+    <hyperlink ref="L8" r:id="rId21" xr:uid="{081455DA-B87F-47D2-AB25-BA3A635C1352}"/>
+    <hyperlink ref="L7" r:id="rId22" xr:uid="{A2837E98-DB96-420C-BDFF-7C55DBDAC86F}"/>
+    <hyperlink ref="L6" r:id="rId23" xr:uid="{5486AFF9-A316-4F6C-8C32-7BC38062E511}"/>
+    <hyperlink ref="L5" r:id="rId24" xr:uid="{D44BD7AA-8277-4C14-B1E3-AEB0BBCFE79D}"/>
+    <hyperlink ref="L4" r:id="rId25" xr:uid="{2DFBF93B-99AF-41D2-87B7-C423E5851D12}"/>
+    <hyperlink ref="L3" r:id="rId26" xr:uid="{907CDA17-31D9-4CC9-AAA2-C77E3F32DCE9}"/>
+    <hyperlink ref="L2" r:id="rId27" xr:uid="{1B021039-0959-46C0-A061-76F250D32C55}"/>
+    <hyperlink ref="L19" r:id="rId28" xr:uid="{8247FD88-1371-44C7-A601-A52FA6BD25B3}"/>
+    <hyperlink ref="L34" r:id="rId29" xr:uid="{EC6E2E4F-7CCC-4158-89E0-06F25A493D34}"/>
+    <hyperlink ref="L33" r:id="rId30" xr:uid="{0703B97E-FC86-4EF1-B6E7-4A5734C5CB7D}"/>
+    <hyperlink ref="L32" r:id="rId31" xr:uid="{5B97BFDC-E863-4BDB-B983-C5FD608CEFB4}"/>
+    <hyperlink ref="L36" r:id="rId32" xr:uid="{41D4AFBB-91CD-4EF0-AC66-0546D3D97838}"/>
+    <hyperlink ref="L35" r:id="rId33" xr:uid="{E44099FF-1B8E-4B38-9BE3-4FD191D4273B}"/>
+    <hyperlink ref="L43" r:id="rId34" xr:uid="{BC3498AF-E6E0-4A79-A360-3455B91F49EE}"/>
+    <hyperlink ref="L37" r:id="rId35" xr:uid="{598DD894-F900-419D-A3C2-A860C745B615}"/>
+    <hyperlink ref="L72" r:id="rId36" xr:uid="{CB53F702-DE69-43E5-BF2A-93044BB24552}"/>
+    <hyperlink ref="L77" r:id="rId37" xr:uid="{6769CC53-79E7-4F64-86CD-D92AFC7E20C0}"/>
+    <hyperlink ref="L100" r:id="rId38" display="http://172.16.238.64:8015/15290001120001/DGR2203/B_FScan" xr:uid="{83B19AC3-668D-425D-8422-5B36234BAD96}"/>
+    <hyperlink ref="L135" r:id="rId39" xr:uid="{8090CEBA-BEE5-4E0F-8D06-6EBA44732754}"/>
+    <hyperlink ref="L163" r:id="rId40" xr:uid="{1DA01A38-0EAA-4681-977F-A6AF35C53703}"/>
+    <hyperlink ref="L97" r:id="rId41" display="http://172.16.238.64:8015/15290001120001/EM/E_QueryDeviceInfo" xr:uid="{644FC5FD-238D-4D23-9712-2B88E6617F48}"/>
+    <hyperlink ref="L127" r:id="rId42" xr:uid="{D1793EF1-D0F0-48BA-8F15-4085256EB965}"/>
+    <hyperlink ref="L125" r:id="rId43" xr:uid="{031EA670-EA3E-4A8C-9089-CB7B41EC7E05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId44"/>
